--- a/src/evaluation/data/processed/RES_accessibility_based_model_travel_time_from_sample_to_hospital.xlsx
+++ b/src/evaluation/data/processed/RES_accessibility_based_model_travel_time_from_sample_to_hospital.xlsx
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.51812201000738</v>
+        <v>49.495769</v>
       </c>
       <c r="F7" t="n">
-        <v>6.446744142481315</v>
+        <v>6.596771</v>
       </c>
       <c r="G7" t="n">
-        <v>16.42</v>
+        <v>30.04</v>
       </c>
       <c r="H7" t="n">
-        <v>4.21</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="8">
@@ -704,7 +704,7 @@
         <v>6.631578</v>
       </c>
       <c r="G9" t="n">
-        <v>11.96</v>
+        <v>11.97</v>
       </c>
       <c r="H9" t="n">
         <v>11.2</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.47310911352534</v>
+        <v>49.4802335</v>
       </c>
       <c r="F10" t="n">
-        <v>6.784165134154136</v>
+        <v>6.7810458</v>
       </c>
       <c r="G10" t="n">
-        <v>12.63</v>
+        <v>12.69</v>
       </c>
       <c r="H10" t="n">
-        <v>7.24</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.60210042480619</v>
+        <v>49.537868</v>
       </c>
       <c r="F11" t="n">
-        <v>6.884531786009908</v>
+        <v>6.88934</v>
       </c>
       <c r="G11" t="n">
-        <v>8.74</v>
+        <v>9.16</v>
       </c>
       <c r="H11" t="n">
-        <v>5.31</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="12">
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>49.35501803983004</v>
+        <v>49.412574</v>
       </c>
       <c r="F12" t="n">
-        <v>7.015709291683912</v>
+        <v>6.909871</v>
       </c>
       <c r="G12" t="n">
-        <v>14.57</v>
+        <v>18.12</v>
       </c>
       <c r="H12" t="n">
-        <v>13.54</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="13">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49.35501803983004</v>
+        <v>49.4668626</v>
       </c>
       <c r="F13" t="n">
-        <v>7.015709291683912</v>
+        <v>7.0713505</v>
       </c>
       <c r="G13" t="n">
-        <v>17.81</v>
+        <v>18.5</v>
       </c>
       <c r="H13" t="n">
-        <v>20.64</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="14">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49.453979</v>
+        <v>49.4668626</v>
       </c>
       <c r="F14" t="n">
-        <v>7.178492</v>
+        <v>7.0713505</v>
       </c>
       <c r="G14" t="n">
-        <v>17.46</v>
+        <v>20.67</v>
       </c>
       <c r="H14" t="n">
-        <v>10.75</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="15">
@@ -1064,7 +1064,7 @@
         <v>6.88979</v>
       </c>
       <c r="G21" t="n">
-        <v>10.95</v>
+        <v>11.06</v>
       </c>
       <c r="H21" t="n">
         <v>6.04</v>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.153009</v>
+        <v>49.1651693</v>
       </c>
       <c r="F22" t="n">
-        <v>7.048336</v>
+        <v>7.1567149</v>
       </c>
       <c r="G22" t="n">
-        <v>19.98</v>
+        <v>12.48</v>
       </c>
       <c r="H22" t="n">
-        <v>10.97</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49.290552</v>
+        <v>49.1847475</v>
       </c>
       <c r="F23" t="n">
-        <v>7.113175</v>
+        <v>7.1613748</v>
       </c>
       <c r="G23" t="n">
-        <v>26.42</v>
+        <v>14.19</v>
       </c>
       <c r="H23" t="n">
-        <v>13.56</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="24">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49.37248449372082</v>
+        <v>49.308199</v>
       </c>
       <c r="F26" t="n">
-        <v>7.350777489274446</v>
+        <v>7.351777</v>
       </c>
       <c r="G26" t="n">
-        <v>20.54</v>
+        <v>19.25</v>
       </c>
       <c r="H26" t="n">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.537868</v>
+        <v>49.5309587</v>
       </c>
       <c r="F27" t="n">
-        <v>6.88934</v>
+        <v>6.9937572</v>
       </c>
       <c r="G27" t="n">
-        <v>13.41</v>
+        <v>7.83</v>
       </c>
       <c r="H27" t="n">
-        <v>7.69</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="28">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.51939194606232</v>
+        <v>49.5309587</v>
       </c>
       <c r="F28" t="n">
-        <v>7.11468832097552</v>
+        <v>6.9937572</v>
       </c>
       <c r="G28" t="n">
-        <v>17.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>10.33</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="29">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49.51939194606232</v>
+        <v>49.5624286</v>
       </c>
       <c r="F29" t="n">
-        <v>7.11468832097552</v>
+        <v>7.0919231</v>
       </c>
       <c r="G29" t="n">
-        <v>3.54</v>
+        <v>14.45</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="30">
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49.51939194606232</v>
+        <v>49.5624286</v>
       </c>
       <c r="F30" t="n">
-        <v>7.11468832097552</v>
+        <v>7.0919231</v>
       </c>
       <c r="G30" t="n">
-        <v>8.279999999999999</v>
+        <v>15.67</v>
       </c>
       <c r="H30" t="n">
-        <v>4.92</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="31">
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49.51939194606232</v>
+        <v>49.5624286</v>
       </c>
       <c r="F31" t="n">
-        <v>7.11468832097552</v>
+        <v>7.0919231</v>
       </c>
       <c r="G31" t="n">
-        <v>19.88</v>
+        <v>21.45</v>
       </c>
       <c r="H31" t="n">
-        <v>15.56</v>
+        <v>16.01</v>
       </c>
     </row>
   </sheetData>
